--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486421_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486421_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0226</v>
+        <v>3.7634</v>
       </c>
       <c r="E2" t="n">
-        <v>2.132</v>
+        <v>4.0634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8905999999999999</v>
+        <v>-0.2999</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9316</v>
+        <v>2.7816</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7451</v>
+        <v>0.6843</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1866</v>
+        <v>2.0974</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2894</v>
+        <v>4.0989</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9125</v>
+        <v>1.5147</v>
       </c>
       <c r="L2" t="n">
-        <v>1.377</v>
+        <v>2.5843</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6422</v>
+        <v>-1.3173</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1674</v>
+        <v>-0.8304</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8096</v>
+        <v>-0.4869</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R2" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1732</v>
+        <v>0.4359</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1476</v>
+        <v>0.2716</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0256</v>
+        <v>0.1643</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6472</v>
+        <v>1.6334</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.0854</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6472</v>
+        <v>-0.452</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7605</v>
+        <v>3.5911</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7282</v>
+        <v>1.3123</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0322</v>
+        <v>2.2788</v>
       </c>
       <c r="G3" t="n">
         <v>0.6863</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9231</v>
+        <v>-0.0925</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0959</v>
+        <v>-0.5119</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1728</v>
+        <v>0.4194</v>
       </c>
       <c r="V3" t="n">
         <v>4.5199</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.747</v>
+        <v>2.4013</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3243</v>
+        <v>1.4182</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5773</v>
+        <v>0.9831</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7816</v>
+        <v>2.9316</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6843</v>
+        <v>0.7451</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0974</v>
+        <v>2.1866</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0989</v>
+        <v>2.2894</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5147</v>
+        <v>0.9125</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5843</v>
+        <v>1.377</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3173</v>
+        <v>0.6422</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8304</v>
+        <v>-0.1674</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4869</v>
+        <v>0.8096</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5805</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4675</v>
+        <v>0.4338</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1131</v>
+        <v>0.1181</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6334</v>
+        <v>-0.6472</v>
       </c>
       <c r="W4" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.452</v>
+        <v>-0.6472</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2814</v>
+        <v>1.1161</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3858</v>
+        <v>3.2993</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1044</v>
+        <v>-2.1832</v>
       </c>
       <c r="G5" t="n">
         <v>3.2032</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6167</v>
+        <v>1.4513</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3942</v>
+        <v>0.3076</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2225</v>
+        <v>1.1437</v>
       </c>
       <c r="V5" t="n">
         <v>-4.191</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3676</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8138</v>
+        <v>0.5037</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.3073</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5886</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3461</v>
+        <v>0.7895</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5432</v>
+        <v>0.2331</v>
       </c>
       <c r="U6" t="n">
-        <v>0.803</v>
+        <v>0.5564</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9923</v>
+        <v>0.606</v>
       </c>
       <c r="E7" t="n">
-        <v>0.833</v>
+        <v>0.2309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1593</v>
+        <v>0.3751</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2648</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2795</v>
+        <v>0.8932</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8736</v>
+        <v>0.2716</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4058</v>
+        <v>0.6216</v>
       </c>
       <c r="V7" t="n">
         <v>0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1664</v>
+        <v>0.5624</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8045</v>
+        <v>1.8861</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9708</v>
+        <v>-1.3237</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6091</v>
+        <v>1.4384</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9094</v>
+        <v>0.1276</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3004</v>
+        <v>1.3108</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9294</v>
+        <v>1.386</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6784</v>
+        <v>0.3134</v>
       </c>
       <c r="L8" t="n">
-        <v>0.251</v>
+        <v>1.0726</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3204</v>
+        <v>0.0524</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2311</v>
+        <v>-0.1858</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5514</v>
+        <v>0.2382</v>
       </c>
       <c r="P8" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3203</v>
+        <v>0.3133</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.125</v>
+        <v>0.1526</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1953</v>
+        <v>0.1607</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3252</v>
+        <v>-2.7119</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3252</v>
+        <v>-3.2769</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3034</v>
+        <v>0.168</v>
       </c>
       <c r="E9" t="n">
-        <v>0.439</v>
+        <v>0.9847</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.8167</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6091</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.362</v>
+        <v>0.9094</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9865</v>
+        <v>-0.3004</v>
       </c>
       <c r="J9" t="n">
-        <v>0.725</v>
+        <v>0.9294</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0365</v>
+        <v>0.6784</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6885</v>
+        <v>0.251</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1004</v>
+        <v>-0.3204</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3985</v>
+        <v>0.2311</v>
       </c>
       <c r="O9" t="n">
-        <v>0.298</v>
+        <v>-0.5514</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.346</v>
+        <v>0.0141</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0553</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2775</v>
+        <v>-0.0412</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.017</v>
+        <v>-1.3252</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.017</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6228</v>
+        <v>0.0194</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8551</v>
+        <v>0.731</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4779</v>
+        <v>-0.7116</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4384</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1276</v>
+        <v>-0.362</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3108</v>
+        <v>0.9865</v>
       </c>
       <c r="J10" t="n">
-        <v>1.386</v>
+        <v>0.725</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3134</v>
+        <v>0.0365</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0726</v>
+        <v>0.6885</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0524</v>
+        <v>-0.1004</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1858</v>
+        <v>-0.3985</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2382</v>
+        <v>0.298</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8718</v>
+        <v>-0.0231</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8784</v>
+        <v>0.2235</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0066</v>
+        <v>-0.2466</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7119</v>
+        <v>-1.017</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.2769</v>
+        <v>-1.017</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.979</v>
+        <v>-0.9722</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5863</v>
+        <v>-0.5178</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3928</v>
+        <v>-0.4544</v>
       </c>
       <c r="G11" t="n">
         <v>0.7043</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0531</v>
+        <v>-0.0463</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2055</v>
+        <v>-0.137</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1524</v>
+        <v>0.0907</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7602</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4737</v>
+        <v>-1.413</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9773</v>
+        <v>-2.1323</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5036</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>0.8195</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1181</v>
+        <v>-0.0574</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1406</v>
+        <v>-0.0144</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2587</v>
+        <v>-0.043</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626100000000001</v>
+        <v>10.6535</v>
       </c>
       <c r="E13" t="n">
-        <v>10.7521</v>
+        <v>11.7795</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.126</v>
+        <v>-1.1259</v>
       </c>
       <c r="G13" t="n">
         <v>12.9451</v>
@@ -1438,7 +1438,7 @@
         <v>4.2276</v>
       </c>
       <c r="I13" t="n">
-        <v>8.717599999999999</v>
+        <v>8.717600000000001</v>
       </c>
       <c r="J13" t="n">
         <v>14.0299</v>
@@ -1456,7 +1456,7 @@
         <v>-0.6862</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3987000000000001</v>
+        <v>-0.3987</v>
       </c>
       <c r="P13" t="n">
         <v>-1.0875</v>
@@ -1468,10 +1468,10 @@
         <v>13.0504</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2026</v>
+        <v>4.2299</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2583999999999999</v>
+        <v>1.2858</v>
       </c>
       <c r="U13" t="n">
         <v>2.9441</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6995</v>
+        <v>2.7522</v>
       </c>
       <c r="E14" t="n">
-        <v>1.912</v>
+        <v>2.2472</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7875</v>
+        <v>0.505</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9114</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0618</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9469</v>
+        <v>-0.6117</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8852</v>
+        <v>0.6026</v>
       </c>
       <c r="V14" t="n">
         <v>3.0202</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4253</v>
+        <v>0.9475</v>
       </c>
       <c r="E15" t="n">
-        <v>3.259</v>
+        <v>2.812</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8337</v>
+        <v>-1.8645</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9479</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4385</v>
+        <v>-0.0394</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2692</v>
+        <v>-0.1778</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1693</v>
+        <v>0.1385</v>
       </c>
       <c r="V15" t="n">
         <v>1.4997</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7016</v>
+        <v>-0.0858</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4492</v>
+        <v>-0.3331</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2525</v>
+        <v>0.2474</v>
       </c>
       <c r="G16" t="n">
         <v>-1.6567</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8358</v>
+        <v>0.0484</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6682</v>
+        <v>-0.1142</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1676</v>
+        <v>0.1625</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2022</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7266</v>
+        <v>1.0579</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9288</v>
+        <v>-1.8285</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6239</v>
+        <v>-0.4605</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4288</v>
+        <v>0.3467</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0527</v>
+        <v>-0.8072</v>
       </c>
       <c r="J17" t="n">
-        <v>1.009</v>
+        <v>0.7127</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8942</v>
+        <v>0.8641</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1147</v>
+        <v>-0.1514</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6328</v>
+        <v>-1.1732</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4654</v>
+        <v>-0.5173</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1674</v>
+        <v>-0.6558</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3118</v>
+        <v>-0.2004</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8051</v>
+        <v>-0.4999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4933</v>
+        <v>0.2995</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3252</v>
+        <v>0.7602</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.0202</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3252</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4592</v>
+        <v>-1.8304</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6108</v>
+        <v>-0.0557</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.07</v>
+        <v>-1.7747</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4605</v>
+        <v>-0.6239</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3467</v>
+        <v>0.4288</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8072</v>
+        <v>-1.0527</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7127</v>
+        <v>1.009</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8641</v>
+        <v>0.8942</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1514</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1732</v>
+        <v>-1.6328</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5173</v>
+        <v>-0.4654</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6558</v>
+        <v>-1.1674</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8889</v>
+        <v>-0.3163</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9469</v>
+        <v>0.0228</v>
       </c>
       <c r="U18" t="n">
-        <v>0.058</v>
+        <v>-0.3392</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7602</v>
+        <v>-1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>3.0202</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2599</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1797</v>
+        <v>-1.9739</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2905</v>
+        <v>-0.5289</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8893</v>
+        <v>-1.4451</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8768</v>
+        <v>0.6443</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2043</v>
+        <v>-0.8817</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6725</v>
+        <v>1.526</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.542</v>
+        <v>2.8159</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8879</v>
+        <v>-0.5134</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3459</v>
+        <v>3.3293</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3348</v>
+        <v>-2.1716</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3164</v>
+        <v>-0.3683</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0184</v>
+        <v>-1.8033</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>2.6101</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0446</v>
+        <v>-0.6405</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2091</v>
+        <v>-0.8424</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1645</v>
+        <v>0.2019</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0.7602</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.695</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6933</v>
+        <v>-2.2607</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9759</v>
+        <v>-0.4022</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7174</v>
+        <v>-1.8584</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6443</v>
+        <v>-1.8768</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8817</v>
+        <v>-1.2043</v>
       </c>
       <c r="I20" t="n">
-        <v>1.526</v>
+        <v>-0.6725</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8159</v>
+        <v>-0.542</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5134</v>
+        <v>-0.8879</v>
       </c>
       <c r="L20" t="n">
-        <v>3.3293</v>
+        <v>0.3459</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1716</v>
+        <v>-1.3348</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3683</v>
+        <v>-0.3164</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8033</v>
+        <v>-1.0184</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6101</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3598</v>
+        <v>-0.0363</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2894</v>
+        <v>0.0973</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0704</v>
+        <v>-0.1337</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0854</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0102</v>
+        <v>-2.5324</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5857</v>
+        <v>-2.1387</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4245</v>
+        <v>-0.3937</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9655</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8495</v>
+        <v>-0.3716</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.233</v>
+        <v>-0.2022</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9079</v>
+        <v>-3.127</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9795</v>
+        <v>-1.5325</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9284</v>
+        <v>-1.5944</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1466</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6732</v>
+        <v>-0.8923</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0959</v>
+        <v>-0.6489</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5773</v>
+        <v>-0.2434</v>
       </c>
       <c r="V22" t="n">
         <v>3.5645</v>
@@ -2203,25 +2203,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.626099999999999</v>
+        <v>-8.8812</v>
       </c>
       <c r="E23" t="n">
-        <v>1.125999999999999</v>
+        <v>1.126</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.7521</v>
+        <v>-10.0069</v>
       </c>
       <c r="G23" t="n">
         <v>-12.945</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.227499999999999</v>
+        <v>-4.2275</v>
       </c>
       <c r="I23" t="n">
         <v>-8.717600000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>1.085</v>
+        <v>1.084999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>0.6862</v>
@@ -2248,13 +2248,13 @@
         <v>14.1377</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.2025</v>
+        <v>-2.4574</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.944</v>
+        <v>-2.9442</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2584000000000001</v>
+        <v>0.4865000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>5.434</v>
